--- a/creative-block/src/app/search/forum/ForumDatabase.xlsx
+++ b/creative-block/src/app/search/forum/ForumDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows\System32\Team25_CreativeBlock\creative-block\src\app\search\forum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC06265-F9EE-4D19-A470-173D69FABA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425F9D1F-050B-4B53-A982-CBDC0AE00E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CC5E6EC3-2E48-4410-AE51-8943AF8DFE6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Entry Id</t>
   </si>
@@ -84,6 +84,30 @@
   </si>
   <si>
     <t>A video tutorial on all the basic things you need to start crocheting!</t>
+  </si>
+  <si>
+    <t>leebruton</t>
+  </si>
+  <si>
+    <t>Good starter projects for knitting?</t>
+  </si>
+  <si>
+    <t>Knitting</t>
+  </si>
+  <si>
+    <t>I'm new to knitting, help!</t>
+  </si>
+  <si>
+    <t>What should I start with, crochet or knitting?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I really want to make winter gear, but I don't know the best way to do it. </t>
+  </si>
+  <si>
+    <t>Best fabric for clothing?</t>
+  </si>
+  <si>
+    <t>What's the best fabric to use as a beginner in clothing making?</t>
   </si>
 </sst>
 </file>
@@ -456,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B547C75-1E53-45A1-B52D-8B1AD52AFE56}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -531,6 +555,84 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46121</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46121</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46121</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D11" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
